--- a/sales.xlsx
+++ b/sales.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mainnnn\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mainnnn\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E146F12-466A-4FC2-A1D7-5BA5BED840A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6B87FF-7891-4B80-9942-7D5443E736B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C48ADF97-2129-4F76-A359-7447CC274021}"/>
   </bookViews>
@@ -37,12 +37,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>id</t>
   </si>
   <si>
     <t>Sales</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -394,127 +397,186 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F799AC-DBB8-4437-8C8D-48F954D3DF2D}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>725</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C2">
+        <f ca="1">RANDBETWEEN(0,1111)</f>
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>430</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C3">
+        <f t="shared" ref="C3:C15" ca="1" si="0">RANDBETWEEN(0,1111)</f>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>551</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C4">
+        <f t="shared" ca="1" si="0"/>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C5">
+        <f t="shared" ca="1" si="0"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>390</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C6">
+        <f t="shared" ca="1" si="0"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>856</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C7">
+        <f t="shared" ca="1" si="0"/>
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>615</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <f t="shared" ca="1" si="0"/>
+        <v>848</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>903</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C9">
+        <f t="shared" ca="1" si="0"/>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>685</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C10">
+        <f t="shared" ca="1" si="0"/>
+        <v>511</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>400</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C11">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>949</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C12">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>89</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C13">
+        <f t="shared" ca="1" si="0"/>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>194</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C14">
+        <f t="shared" ca="1" si="0"/>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>672</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ca="1" si="0"/>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
